--- a/grupos/5APV - Estadisticos 20241.xlsx
+++ b/grupos/5APV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="51">
   <si>
     <t>Materia</t>
   </si>
@@ -146,21 +146,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Morales Estrada Adilene</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Sánchez Sánchez Miguel</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Sánchez Sánchez Miguel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -171,21 +171,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
   </si>
 </sst>
 </file>
@@ -696,19 +681,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -732,13 +717,13 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>5</v>
@@ -770,22 +755,22 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -806,22 +791,22 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>10</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -847,22 +832,22 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -892,10 +877,10 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -924,22 +909,22 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -960,19 +945,19 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>10</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1001,22 +986,22 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1043,13 +1028,13 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1078,22 +1063,22 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1117,19 +1102,19 @@
         <v>6</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1155,22 +1140,22 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1191,19 +1176,19 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1232,22 +1217,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1274,13 +1259,13 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1309,22 +1294,22 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1348,7 +1333,7 @@
         <v>5</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>5</v>
@@ -1386,22 +1371,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1422,7 +1407,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1431,10 +1416,10 @@
         <v>10</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1463,22 +1448,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1499,19 +1484,19 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1540,22 +1525,22 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1576,7 +1561,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1588,10 +1573,10 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1617,22 +1602,22 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1659,16 +1644,16 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1694,22 +1679,22 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1733,16 +1718,16 @@
         <v>8</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1771,22 +1756,22 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1816,7 +1801,7 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -1851,19 +1836,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1887,13 +1872,13 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>5</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -1925,22 +1910,22 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -1964,7 +1949,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2005,19 +1990,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2041,10 +2026,10 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2192,16 +2177,16 @@
         <v>85</v>
       </c>
       <c r="I4">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="J4">
         <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -2210,16 +2195,16 @@
         <v>85</v>
       </c>
       <c r="O4">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="P4">
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -2248,7 +2233,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -2260,13 +2245,13 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2278,7 +2263,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -2307,37 +2292,37 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I6">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M6">
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="O6">
-        <v>96.7</v>
+        <v>95</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -2366,10 +2351,10 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I7">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -2378,16 +2363,16 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M7">
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O7">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -2396,7 +2381,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -2425,16 +2410,16 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="I8">
-        <v>93.3</v>
+        <v>88.3</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -2443,16 +2428,16 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="O8">
-        <v>93.3</v>
+        <v>88.3</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -2484,37 +2469,37 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="I9">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M9">
         <v>100</v>
       </c>
       <c r="N9">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="O9">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -2546,7 +2531,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -2564,7 +2549,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -2605,7 +2590,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -2623,7 +2608,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -2661,37 +2646,37 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="I12">
-        <v>76.7</v>
+        <v>86.7</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="O12">
-        <v>76.7</v>
+        <v>86.7</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -2720,7 +2705,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -2738,7 +2723,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -2779,7 +2764,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -2797,7 +2782,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -2841,7 +2826,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -2859,7 +2844,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -2897,7 +2882,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -2915,7 +2900,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -2956,37 +2941,37 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -3015,16 +3000,16 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I18">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -3033,16 +3018,16 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="O18">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -3074,13 +3059,13 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -3092,13 +3077,13 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -3133,13 +3118,13 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I20">
         <v>100</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -3151,13 +3136,13 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -3192,7 +3177,7 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="I21">
         <v>100</v>
@@ -3210,7 +3195,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -3282,7 +3267,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>42</v>
@@ -3291,19 +3276,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>55.6</v>
+        <v>72.2</v>
       </c>
       <c r="G2" s="2">
-        <v>44.4</v>
+        <v>27.8</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3317,25 +3302,25 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3">
         <v>18</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>61.1</v>
+        <v>72.2</v>
       </c>
       <c r="G3" s="2">
-        <v>38.9</v>
+        <v>27.8</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3346,7 +3331,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>43</v>
@@ -3355,19 +3340,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>66.7</v>
+        <v>72.2</v>
       </c>
       <c r="G4" s="2">
-        <v>33.3</v>
+        <v>27.8</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3399,7 +3384,7 @@
         <v>16.7</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3410,7 +3395,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>45</v>
@@ -3431,7 +3416,7 @@
         <v>5.6</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3442,7 +3427,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>46</v>
@@ -3451,19 +3436,19 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3513,7 +3498,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3543,75 +3528,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920264</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920264</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920271</v>
-      </c>
-      <c r="B4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5APV - Estadisticos 20241.xlsx
+++ b/grupos/5APV - Estadisticos 20241.xlsx
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I4">
         <v>7</v>
@@ -1833,7 +1833,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>10</v>
@@ -1987,7 +1987,7 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>6</v>
@@ -2023,7 +2023,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -3384,7 +3384,7 @@
         <v>16.7</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>

--- a/grupos/5APV - Estadisticos 20241.xlsx
+++ b/grupos/5APV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="65">
   <si>
     <t>Materia</t>
   </si>
@@ -171,6 +171,48 @@
   </si>
   <si>
     <t>Nombres</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
   </si>
 </sst>
 </file>
@@ -3498,7 +3540,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3528,6 +3570,443 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920396</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920396</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920396</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920396</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920405</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920405</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920405</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920405</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920279</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920279</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920279</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920279</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920133</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920133</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>21330051920133</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920133</v>
+      </c>
+      <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920395</v>
+      </c>
+      <c r="B18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920395</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920395</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5APV - Estadisticos 20241.xlsx
+++ b/grupos/5APV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="65">
   <si>
     <t>Materia</t>
   </si>
@@ -149,18 +149,18 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Morales Estrada Adilene</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
+    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>Sánchez Sánchez Miguel</t>
   </si>
   <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -173,43 +173,43 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
     <t>SOTO</t>
   </si>
   <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
     <t>GALINDO</t>
   </si>
   <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
+  </si>
+  <si>
     <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
   </si>
   <si>
     <t>BRANDON</t>
@@ -741,16 +741,16 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -762,13 +762,13 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -818,16 +818,16 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -895,16 +895,16 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -916,13 +916,13 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -972,16 +972,16 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1049,16 +1049,16 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1067,7 +1067,7 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1126,16 +1126,16 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1147,13 +1147,13 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1203,16 +1203,16 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1224,7 +1224,7 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>10</v>
@@ -1280,16 +1280,16 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1304,7 +1304,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1357,16 +1357,16 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1378,13 +1378,13 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1434,16 +1434,16 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1511,16 +1511,16 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1532,7 +1532,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1588,16 +1588,16 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1615,7 +1615,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1665,16 +1665,16 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1686,7 +1686,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1742,16 +1742,16 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1763,7 +1763,7 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -1819,16 +1819,16 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -1840,13 +1840,13 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1896,16 +1896,16 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -1914,16 +1914,16 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -1973,16 +1973,16 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -1994,13 +1994,13 @@
         <v>8</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>7</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2050,16 +2050,16 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2077,7 +2077,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2237,16 +2237,16 @@
         <v>85</v>
       </c>
       <c r="O4">
-        <v>86.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="Q4">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="R4">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -2299,13 +2299,13 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q5">
         <v>100</v>
       </c>
       <c r="R5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -2355,16 +2355,16 @@
         <v>92.5</v>
       </c>
       <c r="O6">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P6">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q6">
         <v>100</v>
       </c>
       <c r="R6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -2414,16 +2414,16 @@
         <v>97.5</v>
       </c>
       <c r="O7">
-        <v>83.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="Q7">
         <v>100</v>
       </c>
       <c r="R7">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -2473,16 +2473,16 @@
         <v>92.5</v>
       </c>
       <c r="O8">
-        <v>88.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P8">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="Q8">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -2532,16 +2532,16 @@
         <v>92.5</v>
       </c>
       <c r="O9">
-        <v>88.3</v>
+        <v>83.3</v>
       </c>
       <c r="P9">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="Q9">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="R9">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -2591,7 +2591,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -2650,7 +2650,7 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -2709,16 +2709,16 @@
         <v>82.5</v>
       </c>
       <c r="O12">
-        <v>86.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P12">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q12">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="R12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -2886,7 +2886,7 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -2954,7 +2954,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3007,13 +3007,13 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -3063,16 +3063,16 @@
         <v>85</v>
       </c>
       <c r="O18">
-        <v>98.3</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q18">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -3122,16 +3122,16 @@
         <v>90</v>
       </c>
       <c r="O19">
-        <v>98.3</v>
+        <v>94.8</v>
       </c>
       <c r="P19">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3181,16 +3181,16 @@
         <v>90</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="P20">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -3249,7 +3249,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -3350,19 +3350,19 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>72.2</v>
+        <v>83.3</v>
       </c>
       <c r="G3" s="2">
-        <v>27.8</v>
+        <v>16.7</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3373,28 +3373,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>18</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>44</v>
@@ -3414,19 +3414,19 @@
         <v>18</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3437,7 +3437,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>45</v>
@@ -3446,19 +3446,19 @@
         <v>18</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>46</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3540,7 +3540,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3572,19 +3572,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920396</v>
+        <v>22330051920405</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
         <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>43</v>
@@ -3595,22 +3595,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920396</v>
+        <v>22330051920405</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3618,19 +3618,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920396</v>
+        <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
         <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>43</v>
@@ -3641,16 +3641,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920396</v>
+        <v>22330051920279</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3664,22 +3664,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920405</v>
+        <v>21330051920133</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3687,22 +3687,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920405</v>
+        <v>21330051920133</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3710,22 +3710,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920405</v>
+        <v>21330051920396</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -3733,16 +3733,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920405</v>
+        <v>22330051920395</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -3751,259 +3751,6 @@
         <v>42</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920279</v>
-      </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920279</v>
-      </c>
-      <c r="B11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920279</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920279</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920133</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920133</v>
-      </c>
-      <c r="B15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920133</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920133</v>
-      </c>
-      <c r="B17" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920395</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920395</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920395</v>
-      </c>
-      <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20241.xlsx
+++ b/grupos/5APV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
   <si>
     <t>Materia</t>
   </si>
@@ -173,19 +173,25 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>GALINDO</t>
   </si>
   <si>
     <t>JOSE</t>
@@ -194,25 +200,19 @@
     <t>MONTIEL</t>
   </si>
   <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
+    <t>IGNACIO</t>
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
   </si>
   <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
     <t>HECTOR MISAEL</t>
   </si>
   <si>
     <t>CESAR DANIEL</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
   </si>
 </sst>
 </file>
@@ -738,7 +738,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>9</v>
@@ -756,7 +756,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -815,7 +815,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -833,7 +833,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>9</v>
@@ -1046,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>10</v>
@@ -1218,7 +1218,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1277,7 +1277,7 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1354,7 +1354,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>7</v>
@@ -1372,7 +1372,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -1431,7 +1431,7 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>10</v>
@@ -1508,7 +1508,7 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -1585,7 +1585,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>10</v>
@@ -1662,7 +1662,7 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
         <v>10</v>
@@ -1739,7 +1739,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>8</v>
@@ -1757,7 +1757,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1816,7 +1816,7 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>7</v>
@@ -1834,7 +1834,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -1893,7 +1893,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -1970,7 +1970,7 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -1988,7 +1988,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2047,7 +2047,7 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>8</v>
@@ -2234,7 +2234,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>85</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O4">
         <v>89.59999999999999</v>
@@ -2293,7 +2293,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -2352,7 +2352,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="O6">
         <v>96.90000000000001</v>
@@ -2411,7 +2411,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O7">
         <v>85.40000000000001</v>
@@ -2470,7 +2470,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="O8">
         <v>84.40000000000001</v>
@@ -2529,7 +2529,7 @@
         <v>100</v>
       </c>
       <c r="N9">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="O9">
         <v>83.3</v>
@@ -2706,7 +2706,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O12">
         <v>89.59999999999999</v>
@@ -2765,7 +2765,7 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -2824,7 +2824,7 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -2942,7 +2942,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -3001,7 +3001,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -3060,7 +3060,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O18">
         <v>96.90000000000001</v>
@@ -3119,7 +3119,7 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="O19">
         <v>94.8</v>
@@ -3178,7 +3178,7 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="O20">
         <v>95.8</v>
@@ -3237,7 +3237,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -3350,19 +3350,19 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3540,7 +3540,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3572,22 +3572,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920405</v>
+        <v>21330051920396</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
         <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3598,13 +3598,13 @@
         <v>22330051920405</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3618,22 +3618,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920279</v>
+        <v>22330051920395</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3644,13 +3644,13 @@
         <v>22330051920279</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -3667,90 +3667,21 @@
         <v>21330051920133</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920133</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920396</v>
-      </c>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920395</v>
-      </c>
-      <c r="B9" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5APV - Estadisticos 20241.xlsx
+++ b/grupos/5APV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="51">
   <si>
     <t>Materia</t>
   </si>
@@ -171,48 +171,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>GALINDO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>IGNACIO</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>HECTOR MISAEL</t>
-  </si>
-  <si>
-    <t>CESAR DANIEL</t>
   </si>
 </sst>
 </file>
@@ -753,7 +711,7 @@
         <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -771,7 +729,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -830,7 +788,7 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -907,7 +865,7 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -984,7 +942,7 @@
         <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1061,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>7</v>
@@ -1079,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1138,7 +1096,7 @@
         <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1156,7 +1114,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1215,7 +1173,7 @@
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1292,7 +1250,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1369,7 +1327,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -1387,7 +1345,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1446,7 +1404,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1523,7 +1481,7 @@
         <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1600,7 +1558,7 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1677,7 +1635,7 @@
         <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1754,7 +1712,7 @@
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1831,7 +1789,7 @@
         <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -1849,7 +1807,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1908,7 +1866,7 @@
         <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -1926,7 +1884,7 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1985,7 +1943,7 @@
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>6</v>
@@ -2003,7 +1961,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2062,7 +2020,7 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>7</v>
@@ -3318,19 +3276,19 @@
         <v>18</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>27.8</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3540,7 +3498,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3570,121 +3528,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920396</v>
-      </c>
-      <c r="B2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920405</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920395</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920279</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920133</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
